--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513659_FASEFINALBFFB3_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513659_FASEFINALBFFB3_PROCESSED.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.111800000000001</v>
+        <v>9.339</v>
       </c>
       <c r="E2" t="n">
-        <v>7.2297</v>
+        <v>7.4291</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8821</v>
+        <v>1.9099</v>
       </c>
       <c r="G2" t="n">
         <v>5.8375</v>
@@ -610,13 +610,13 @@
         <v>1.9474</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.2671</v>
+        <v>-1.0399</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.113</v>
+        <v>-0.9137</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1541</v>
+        <v>-0.1262</v>
       </c>
       <c r="V2" t="n">
         <v>3.9573</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3286</v>
+        <v>2.8866</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2182</v>
+        <v>2.9432</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1104</v>
+        <v>-0.0566</v>
       </c>
       <c r="G3" t="n">
         <v>0.3406</v>
@@ -688,13 +688,13 @@
         <v>1.3632</v>
       </c>
       <c r="S3" t="n">
-        <v>0.065</v>
+        <v>-0.377</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.263</v>
+        <v>-0.5381</v>
       </c>
       <c r="U3" t="n">
-        <v>0.328</v>
+        <v>0.161</v>
       </c>
       <c r="V3" t="n">
         <v>1.9494</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. HOGAN</t>
+          <t>J. DOMINGUEZ FRAIZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8817</v>
+        <v>2.3528</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6622</v>
+        <v>1.9338</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2194</v>
+        <v>0.4191</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3281</v>
+        <v>3.7894</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8519</v>
+        <v>-0.0052</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4762</v>
+        <v>3.7946</v>
       </c>
       <c r="J4" t="n">
-        <v>2.8911</v>
+        <v>5.0274</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6479</v>
+        <v>1.7447</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2432</v>
+        <v>3.2826</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5629999999999999</v>
+        <v>-1.238</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.796</v>
+        <v>-1.7499</v>
       </c>
       <c r="O4" t="n">
-        <v>0.233</v>
+        <v>0.5119</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1947</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9737</v>
+        <v>-2.1421</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1684</v>
+        <v>1.3632</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.2517</v>
+        <v>-0.6576</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8657</v>
+        <v>-0.9515</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.386</v>
+        <v>0.2939</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6105</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6105</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. DOMINGUEZ FRAIZ</t>
+          <t>D. HOGAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8512</v>
+        <v>1.9257</v>
       </c>
       <c r="E5" t="n">
-        <v>1.7104</v>
+        <v>1.7619</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1408</v>
+        <v>0.1638</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7894</v>
+        <v>2.3281</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0052</v>
+        <v>1.8519</v>
       </c>
       <c r="I5" t="n">
-        <v>3.7946</v>
+        <v>0.4762</v>
       </c>
       <c r="J5" t="n">
-        <v>5.0274</v>
+        <v>2.8911</v>
       </c>
       <c r="K5" t="n">
-        <v>1.7447</v>
+        <v>2.6479</v>
       </c>
       <c r="L5" t="n">
-        <v>3.2826</v>
+        <v>0.2432</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.238</v>
+        <v>-0.5629999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.7499</v>
+        <v>-0.796</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5119</v>
+        <v>0.233</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.7789</v>
+        <v>0.1947</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.1421</v>
+        <v>-0.9737</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3632</v>
+        <v>1.1684</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1592</v>
+        <v>-1.2077</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.1749</v>
+        <v>-0.766</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0157</v>
+        <v>-0.4416</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.6105</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.6105</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1937</v>
+        <v>1.7788</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7481</v>
+        <v>0.9715</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4456</v>
+        <v>0.8073</v>
       </c>
       <c r="G6" t="n">
         <v>2.0124</v>
@@ -922,13 +922,13 @@
         <v>1.9474</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.697</v>
+        <v>-1.1119</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.1749</v>
+        <v>-0.9515</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5221</v>
+        <v>-0.1604</v>
       </c>
       <c r="V6" t="n">
         <v>0.2941</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8384</v>
+        <v>0.8941</v>
       </c>
       <c r="E7" t="n">
         <v>1.9063</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0679</v>
+        <v>-1.0123</v>
       </c>
       <c r="G7" t="n">
         <v>2.6353</v>
@@ -1000,13 +1000,13 @@
         <v>0.1947</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8221000000000001</v>
+        <v>-0.7665</v>
       </c>
       <c r="T7" t="n">
         <v>-0.4328</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3893</v>
+        <v>-0.3336</v>
       </c>
       <c r="V7" t="n">
         <v>-1.1695</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1515</v>
+        <v>0.1793</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1515</v>
+        <v>0.1793</v>
       </c>
       <c r="G8" t="n">
         <v>0.1329</v>
@@ -1078,13 +1078,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0186</v>
+        <v>0.0464</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0186</v>
+        <v>0.0464</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.052</v>
+        <v>-0.528</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4572</v>
+        <v>-0.7941</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4053</v>
+        <v>0.2661</v>
       </c>
       <c r="G9" t="n">
         <v>1.0849</v>
@@ -1156,13 +1156,13 @@
         <v>0.9737</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.581</v>
+        <v>-1.057</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3249</v>
+        <v>-0.6617</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2561</v>
+        <v>-0.3953</v>
       </c>
       <c r="V9" t="n">
         <v>2.5599</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6332</v>
+        <v>-0.9114</v>
       </c>
       <c r="E10" t="n">
         <v>-0.43</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2032</v>
+        <v>-0.4815</v>
       </c>
       <c r="G10" t="n">
         <v>0.2767</v>
@@ -1234,13 +1234,13 @@
         <v>0.7789</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4356</v>
+        <v>-0.7139</v>
       </c>
       <c r="T10" t="n">
         <v>-0.2473</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1883</v>
+        <v>-0.4665</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2795</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. OLOWOKERE</t>
+          <t>A. CARDITO MARTIN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.7502</v>
+        <v>-4.5803</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.6088</v>
+        <v>-3.9754</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1414</v>
+        <v>-0.6049</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.183</v>
+        <v>-2.7079</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.2575</v>
+        <v>0.294</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.9255</v>
+        <v>-3.0019</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.1029</v>
+        <v>-1.5712</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.1602</v>
+        <v>1.0058</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0572</v>
+        <v>-2.577</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.0801</v>
+        <v>-1.1367</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.0973</v>
+        <v>-0.7118</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9828</v>
+        <v>-0.4249</v>
       </c>
       <c r="P11" t="n">
+        <v>-1.1684</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-1.9474</v>
+      </c>
+      <c r="R11" t="n">
         <v>0.7789</v>
       </c>
-      <c r="Q11" t="n">
-        <v>-1.3632</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.1421</v>
-      </c>
       <c r="S11" t="n">
-        <v>-1.4124</v>
+        <v>-0.704</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.4222</v>
+        <v>-0.4568</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0098</v>
+        <v>-0.2471</v>
       </c>
       <c r="V11" t="n">
-        <v>0.06619999999999999</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2795</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. CARDITO MARTIN</t>
+          <t>M. OLOWOKERE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.9922</v>
+        <v>-4.7889</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.1369</v>
+        <v>-4.2858</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8554</v>
+        <v>-0.5031</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.7079</v>
+        <v>-4.183</v>
       </c>
       <c r="H12" t="n">
-        <v>0.294</v>
+        <v>-3.2575</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.0019</v>
+        <v>-0.9255</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.5712</v>
+        <v>-2.1029</v>
       </c>
       <c r="K12" t="n">
-        <v>1.0058</v>
+        <v>-2.1602</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.577</v>
+        <v>0.0572</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.1367</v>
+        <v>-2.0801</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7118</v>
+        <v>-1.0973</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.4249</v>
+        <v>-0.9828</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1684</v>
+        <v>0.7789</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9474</v>
+        <v>-1.3632</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7789</v>
+        <v>2.1421</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1159</v>
+        <v>-1.4511</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6183</v>
+        <v>-1.0992</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4976</v>
+        <v>-0.3519</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-0.2133</v>
       </c>
     </row>
     <row r="13">
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.929300000000001</v>
+        <v>8.547700000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>6.842000000000003</v>
+        <v>7.460499999999998</v>
       </c>
       <c r="F13" t="n">
-        <v>1.0872</v>
+        <v>1.0871</v>
       </c>
       <c r="G13" t="n">
         <v>11.5469</v>
       </c>
       <c r="H13" t="n">
-        <v>2.178100000000001</v>
+        <v>2.1781</v>
       </c>
       <c r="I13" t="n">
         <v>9.3689</v>
@@ -1468,13 +1468,13 @@
         <v>12.6579</v>
       </c>
       <c r="S13" t="n">
-        <v>-9.6584</v>
+        <v>-9.0402</v>
       </c>
       <c r="T13" t="n">
-        <v>-7.637</v>
+        <v>-7.0186</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.0214</v>
+        <v>-2.0213</v>
       </c>
       <c r="V13" t="n">
         <v>7.9884</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. CALERO BAUTISTA</t>
+          <t>E. LLACER SIMLAT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.7613</v>
+        <v>3.1409</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1832</v>
+        <v>3.3471</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5780999999999999</v>
+        <v>-0.2062</v>
       </c>
       <c r="G14" t="n">
-        <v>2.451</v>
+        <v>2.5115</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.3858</v>
+        <v>1.1533</v>
       </c>
       <c r="I14" t="n">
-        <v>2.8368</v>
+        <v>1.3582</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5036</v>
+        <v>3.7258</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2898</v>
+        <v>3.0125</v>
       </c>
       <c r="L14" t="n">
-        <v>3.7934</v>
+        <v>0.7134</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0526</v>
+        <v>-1.2144</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.096</v>
+        <v>-1.8592</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9565</v>
+        <v>0.6448</v>
       </c>
       <c r="P14" t="n">
-        <v>0.5842000000000001</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q14" t="n">
         <v>-0.9737</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5579</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8809</v>
+        <v>0.8616</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0157</v>
+        <v>0.036</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8966</v>
+        <v>0.8255</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.1548</v>
+        <v>0.1574</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.3311</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.8238</v>
+        <v>-0.4016</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. BEDIA FERRER</t>
+          <t>D. CALERO BAUTISTA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.7178</v>
+        <v>2.7218</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1633</v>
+        <v>2.2828</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4455</v>
+        <v>0.439</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.6357</v>
+        <v>2.451</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0682</v>
+        <v>-0.3858</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.7039</v>
+        <v>2.8368</v>
       </c>
       <c r="J15" t="n">
-        <v>2.6168</v>
+        <v>3.5036</v>
       </c>
       <c r="K15" t="n">
-        <v>1.8063</v>
+        <v>-0.2898</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8105</v>
+        <v>3.7934</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.2525</v>
+        <v>-1.0526</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.7381</v>
+        <v>-0.096</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.5144</v>
+        <v>-0.9565</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.3368</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.0895</v>
+        <v>-0.9737</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7526</v>
+        <v>1.5579</v>
       </c>
       <c r="S15" t="n">
-        <v>4.1941</v>
+        <v>0.8415</v>
       </c>
       <c r="T15" t="n">
-        <v>3.4148</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7792</v>
+        <v>0.7575</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4962</v>
+        <v>-1.1548</v>
       </c>
       <c r="W15" t="n">
-        <v>1.2211</v>
+        <v>-0.3311</v>
       </c>
       <c r="X15" t="n">
-        <v>0.2752</v>
+        <v>-0.8238</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. LLACER SIMLAT</t>
+          <t>L. BLASCO NAVARRO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6749</v>
+        <v>1.019</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0481</v>
+        <v>0.7205</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3732</v>
+        <v>0.2986</v>
       </c>
       <c r="G16" t="n">
-        <v>2.5115</v>
+        <v>-0.6237</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1533</v>
+        <v>0.7703</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3582</v>
+        <v>-1.394</v>
       </c>
       <c r="J16" t="n">
-        <v>3.7258</v>
+        <v>1.5354</v>
       </c>
       <c r="K16" t="n">
-        <v>3.0125</v>
+        <v>1.4215</v>
       </c>
       <c r="L16" t="n">
-        <v>0.7134</v>
+        <v>0.1139</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2144</v>
+        <v>-2.1591</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.8592</v>
+        <v>-0.6513</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6448</v>
+        <v>-1.5078</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3895</v>
+        <v>0.7789</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9737</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5842000000000001</v>
+        <v>1.7526</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3956</v>
+        <v>1.0771</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.263</v>
+        <v>0.1588</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6586</v>
+        <v>0.9183</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1574</v>
+        <v>-0.2133</v>
       </c>
       <c r="W16" t="n">
-        <v>0.5590000000000001</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.4016</v>
+        <v>-0.2133</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. BLASCO NAVARRO</t>
+          <t>A. TERRADES DAROQUI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6171</v>
+        <v>0.6986</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3185</v>
+        <v>0.5662</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2986</v>
+        <v>0.1324</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6237</v>
+        <v>-1.8311</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7703</v>
+        <v>-2.4569</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.394</v>
+        <v>0.6258</v>
       </c>
       <c r="J17" t="n">
-        <v>1.5354</v>
+        <v>-0.0299</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4215</v>
+        <v>-1.2135</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1139</v>
+        <v>1.1836</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.1591</v>
+        <v>-1.8013</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6513</v>
+        <v>-1.2434</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.5078</v>
+        <v>-0.5578</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7789</v>
+        <v>0.9737</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9737</v>
+        <v>-0.1947</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7526</v>
+        <v>1.1684</v>
       </c>
       <c r="S17" t="n">
-        <v>1.6751</v>
+        <v>1.3987</v>
       </c>
       <c r="T17" t="n">
-        <v>0.7568</v>
+        <v>0.5113</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9183</v>
+        <v>0.8874</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2133</v>
+        <v>0.1574</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2795</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2133</v>
+        <v>-0.1221</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. TERRADES DAROQUI</t>
+          <t>J. BEDIA FERRER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.3988</v>
+        <v>0.5087</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7655</v>
+        <v>0.8707</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6333</v>
+        <v>-0.362</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.8311</v>
+        <v>-0.6357</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.4569</v>
+        <v>0.0682</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6258</v>
+        <v>-0.7039</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0299</v>
+        <v>2.6168</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.2135</v>
+        <v>1.8063</v>
       </c>
       <c r="L18" t="n">
-        <v>1.1836</v>
+        <v>0.8105</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.8013</v>
+        <v>-3.2525</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2434</v>
+        <v>-1.7381</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5578</v>
+        <v>-1.5144</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9737</v>
+        <v>-2.3368</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1947</v>
+        <v>-4.0895</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1684</v>
+        <v>1.7526</v>
       </c>
       <c r="S18" t="n">
-        <v>2.0989</v>
+        <v>1.985</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7107</v>
+        <v>1.1223</v>
       </c>
       <c r="U18" t="n">
-        <v>1.3882</v>
+        <v>0.8627</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1574</v>
+        <v>1.4962</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2795</v>
+        <v>1.2211</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1221</v>
+        <v>0.2752</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.0404</v>
+        <v>0.3194</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6579</v>
+        <v>0.1595</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3824</v>
+        <v>0.1598</v>
       </c>
       <c r="G19" t="n">
         <v>-2.5332</v>
@@ -1936,13 +1936,13 @@
         <v>1.7526</v>
       </c>
       <c r="S19" t="n">
-        <v>2.4542</v>
+        <v>1.7332</v>
       </c>
       <c r="T19" t="n">
-        <v>1.066</v>
+        <v>0.5676</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3882</v>
+        <v>1.1656</v>
       </c>
       <c r="V19" t="n">
         <v>-0.4385</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7873</v>
+        <v>-0.7951</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.2521</v>
+        <v>0.5453</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.5351</v>
+        <v>-1.3403</v>
       </c>
       <c r="G20" t="n">
         <v>1.6039</v>
@@ -2014,13 +2014,13 @@
         <v>1.5579</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5596</v>
+        <v>0.4326</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6183</v>
+        <v>0.1791</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0588</v>
+        <v>0.2536</v>
       </c>
       <c r="V20" t="n">
         <v>-2.4421</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.5405</v>
+        <v>-3.5645</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4545</v>
+        <v>-1.7568</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.086</v>
+        <v>-1.8078</v>
       </c>
       <c r="G21" t="n">
         <v>-3.4572</v>
@@ -2092,13 +2092,13 @@
         <v>1.3632</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7513</v>
+        <v>0.2247</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8038999999999999</v>
+        <v>-0.1061</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0526</v>
+        <v>0.3309</v>
       </c>
       <c r="V21" t="n">
         <v>-1.5005</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.0308</v>
+        <v>-5.5603</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.7109</v>
+        <v>-4.2126</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.3199</v>
+        <v>-1.3477</v>
       </c>
       <c r="G22" t="n">
         <v>-2.7202</v>
@@ -2170,13 +2170,13 @@
         <v>1.1684</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0896</v>
+        <v>0.3809</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6183</v>
+        <v>-0.12</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5286999999999999</v>
+        <v>0.5009</v>
       </c>
       <c r="V22" t="n">
         <v>-2.4421</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.7809</v>
+        <v>-6.4179</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.8061</v>
+        <v>-3.61</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.9749</v>
+        <v>-2.8079</v>
       </c>
       <c r="G23" t="n">
         <v>-6.3119</v>
@@ -2248,13 +2248,13 @@
         <v>1.9474</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6399</v>
+        <v>0.7231</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.6077</v>
+        <v>-0.4116</v>
       </c>
       <c r="U23" t="n">
-        <v>0.9678</v>
+        <v>1.1347</v>
       </c>
       <c r="V23" t="n">
         <v>-1.608</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.9292</v>
+        <v>-7.929399999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0871</v>
+        <v>-1.087299999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.8422</v>
+        <v>-6.8421</v>
       </c>
       <c r="G24" t="n">
         <v>-11.5466</v>
@@ -2296,16 +2296,16 @@
         <v>-2.1779</v>
       </c>
       <c r="I24" t="n">
-        <v>-9.3688</v>
+        <v>-9.368799999999998</v>
       </c>
       <c r="J24" t="n">
-        <v>8.255100000000002</v>
+        <v>8.255099999999999</v>
       </c>
       <c r="K24" t="n">
         <v>7.295500000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>0.9597000000000004</v>
+        <v>0.9596999999999996</v>
       </c>
       <c r="M24" t="n">
         <v>-19.8018</v>
@@ -2326,13 +2326,13 @@
         <v>14.6052</v>
       </c>
       <c r="S24" t="n">
-        <v>9.658399999999999</v>
+        <v>9.658400000000002</v>
       </c>
       <c r="T24" t="n">
         <v>2.0214</v>
       </c>
       <c r="U24" t="n">
-        <v>7.637</v>
+        <v>7.6371</v>
       </c>
       <c r="V24" t="n">
         <v>-7.988300000000001</v>
